--- a/data/trans_orig/P78C_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P78C_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba la persona sustentadora principal en 2023</t>
+          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba la persona sustentadora principal en 2023 (tasa de respuesta: 98,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>198312</t>
+          <t>199915</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>231809</t>
+          <t>232231</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>205571</t>
+          <t>205176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>221694</t>
+          <t>221761</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>410860</t>
+          <t>411463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>447540</t>
+          <t>449017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>84,15%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12619</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>12698</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,62 +991,62 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1028</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>3164</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,47 +1104,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>936</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1028</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>936</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20415</t>
+          <t>20942</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8680</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25374</t>
+          <t>25909</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36306</t>
+          <t>36026</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67637</t>
+          <t>66522</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19641</t>
+          <t>19977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34075</t>
+          <t>34453</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60582</t>
+          <t>60882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94536</t>
+          <t>95065</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>385600</t>
+          <t>386969</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>417702</t>
+          <t>418409</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>321096</t>
+          <t>321728</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>337556</t>
+          <t>338141</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>714544</t>
+          <t>715285</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>750323</t>
+          <t>750424</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10756</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29337</t>
+          <t>27759</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7396</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12665</t>
+          <t>12649</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31207</t>
+          <t>32105</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -1864,97 +1864,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2425</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>814</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,02%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,1%</t>
         </is>
       </c>
     </row>
@@ -1977,97 +1977,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2425</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3038</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>586</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>2962</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>2979</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3293</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15164</t>
+          <t>16075</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19116</t>
+          <t>17883</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13657</t>
+          <t>13586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18397</t>
+          <t>18616</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43131</t>
+          <t>42931</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13087</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26902</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35346</t>
+          <t>34704</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61822</t>
+          <t>60712</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>201045</t>
+          <t>200967</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229111</t>
+          <t>227758</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>227035</t>
+          <t>226411</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246789</t>
+          <t>246215</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>435310</t>
+          <t>435929</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>469212</t>
+          <t>467422</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9672</t>
+          <t>9726</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22568</t>
+          <t>23096</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>9796</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13606</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>29507</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>620</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>19067</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10837</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25704</t>
+          <t>26170</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3146,62 +3146,62 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1555</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>1212</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>5808</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1555</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>5321</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25749</t>
+          <t>25969</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47154</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21718</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38953</t>
+          <t>39862</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>51102</t>
+          <t>51983</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>78672</t>
+          <t>80001</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>173722</t>
+          <t>172421</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>212197</t>
+          <t>212039</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>132696</t>
+          <t>129450</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>309371</t>
+          <t>309052</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>285468</t>
+          <t>311518</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>500968</t>
+          <t>500548</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>14950</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>39960</t>
+          <t>41179</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18014</t>
+          <t>16985</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22623</t>
+          <t>20473</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54612</t>
+          <t>53309</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -3793,12 +3793,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20255</t>
+          <t>21185</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>412</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5680</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>23042</t>
+          <t>22242</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>15449</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>214036</t>
+          <t>215750</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>270832</t>
+          <t>244594</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15102</t>
+          <t>15775</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1576</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>20021</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>39547</t>
+          <t>38979</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>67793</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>23395</t>
+          <t>23130</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>59417</t>
+          <t>60130</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>66429</t>
+          <t>63393</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>118828</t>
+          <t>118852</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>114855</t>
+          <t>114551</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>130829</t>
+          <t>130433</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>127786</t>
+          <t>128230</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>139494</t>
+          <t>139464</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>247047</t>
+          <t>246404</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>266686</t>
+          <t>266484</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,12%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12933</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>16522</t>
+          <t>15961</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4623,62 +4623,62 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>803</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>3486</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>4044</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -4701,97 +4701,97 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>1175</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>4128</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>1112</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="S39" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>4510</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>4254</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t>5067</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>13431</t>
+          <t>13415</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4829,12 +4829,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>13082</t>
+          <t>12550</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4884,12 +4884,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>10335</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>22842</t>
+          <t>22029</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>421</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -5040,12 +5040,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>9357</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>20612</t>
+          <t>20724</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>12052</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>15874</t>
+          <t>16173</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>29144</t>
+          <t>29337</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>158791</t>
+          <t>159006</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>184603</t>
+          <t>184589</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>156711</t>
+          <t>156765</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>172647</t>
+          <t>173303</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>322507</t>
+          <t>322825</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>352649</t>
+          <t>351847</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,86%</t>
         </is>
       </c>
     </row>
@@ -5383,12 +5383,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>12265</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>524</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>15131</t>
+          <t>14709</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -5496,97 +5496,97 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>1346</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="R46" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>1187</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -5722,12 +5722,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>24864</t>
+          <t>24158</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>45167</t>
+          <t>42813</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5737,12 +5737,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>13739</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>31065</t>
+          <t>31908</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>51221</t>
+          <t>53517</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -5835,12 +5835,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>361</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -5948,12 +5948,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>27266</t>
+          <t>27919</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>46995</t>
+          <t>46606</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5963,12 +5963,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>17185</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>33127</t>
+          <t>31812</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>49369</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>73039</t>
+          <t>72897</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -6178,12 +6178,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>375155</t>
+          <t>374385</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>419715</t>
+          <t>416435</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6193,12 +6193,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>554406</t>
+          <t>553459</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>670309</t>
+          <t>668686</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>941976</t>
+          <t>939845</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1112845</t>
+          <t>1109504</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,03%</t>
         </is>
       </c>
     </row>
@@ -6291,12 +6291,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>42723</t>
+          <t>43602</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>70551</t>
+          <t>71159</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6306,12 +6306,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>39356</t>
+          <t>39203</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>43466</t>
+          <t>44195</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>105304</t>
+          <t>105070</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -6404,12 +6404,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>13806</t>
+          <t>13736</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6419,12 +6419,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>833</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>8212</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>18914</t>
+          <t>19139</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -6517,12 +6517,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>17610</t>
+          <t>18241</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6552,12 +6552,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>14666</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>28224</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -6630,12 +6630,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>11081</t>
+          <t>12146</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>28210</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6645,12 +6645,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>24869</t>
+          <t>25393</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>19026</t>
+          <t>19204</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>46788</t>
+          <t>47410</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -6743,12 +6743,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>17758</t>
+          <t>17712</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>12523</t>
+          <t>12418</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>26060</t>
+          <t>25571</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -6856,12 +6856,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>42327</t>
+          <t>42863</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>71157</t>
+          <t>72205</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>23304</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>82683</t>
+          <t>82423</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>63752</t>
+          <t>65582</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>138984</t>
+          <t>140170</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -7086,12 +7086,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>164543</t>
+          <t>158936</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>517468</t>
+          <t>517396</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>312767</t>
+          <t>313300</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>348387</t>
+          <t>346508</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>400503</t>
+          <t>372945</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>861914</t>
+          <t>856917</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,44%</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7199,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>53645</t>
+          <t>52523</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>161557</t>
+          <t>162823</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>37452</t>
+          <t>37895</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>59086</t>
+          <t>60242</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>93801</t>
+          <t>82289</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>200667</t>
+          <t>199267</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>9054</t>
+          <t>9973</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>11672</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -7425,12 +7425,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>578774</t>
+          <t>580419</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7440,12 +7440,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>10069</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>715596</t>
+          <t>772532</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>57,19%</t>
         </is>
       </c>
     </row>
@@ -7538,12 +7538,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>9916</t>
+          <t>10171</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>38375</t>
+          <t>37366</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7553,12 +7553,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>19780</t>
+          <t>20568</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>19993</t>
+          <t>19150</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>51747</t>
+          <t>52344</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -7651,12 +7651,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>23219</t>
+          <t>23073</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>23092</t>
+          <t>23515</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -7764,12 +7764,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>47690</t>
+          <t>45001</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>153865</t>
+          <t>153368</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>69290</t>
+          <t>69699</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>97239</t>
+          <t>96166</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7814,12 +7814,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>104213</t>
+          <t>99281</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>237400</t>
+          <t>236144</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -7994,12 +7994,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>1649369</t>
+          <t>1596478</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2276213</t>
+          <t>2276360</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>2104567</t>
+          <t>2075468</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>2371668</t>
+          <t>2364798</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8044,12 +8044,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>3716044</t>
+          <t>3782930</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>4604112</t>
+          <t>4591892</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -8107,12 +8107,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>191004</t>
+          <t>185726</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>278556</t>
+          <t>281936</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8122,12 +8122,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>72429</t>
+          <t>73254</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>113447</t>
+          <t>114745</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8157,12 +8157,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>281965</t>
+          <t>280631</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>382568</t>
+          <t>380516</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -8220,12 +8220,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>25193</t>
+          <t>25435</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8235,12 +8235,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>11395</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8270,12 +8270,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>32399</t>
+          <t>32755</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8305,12 +8305,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -8333,12 +8333,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>27893</t>
+          <t>28073</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>829649</t>
+          <t>953297</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8348,12 +8348,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>25922</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>43497</t>
+          <t>44681</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>1232232</t>
+          <t>1061249</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>86837</t>
+          <t>87237</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>139227</t>
+          <t>139646</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8461,12 +8461,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>58797</t>
+          <t>56850</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>403699</t>
+          <t>403294</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8496,12 +8496,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>167127</t>
+          <t>170672</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>494460</t>
+          <t>553903</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>26318</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>55461</t>
+          <t>54130</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>21807</t>
+          <t>21890</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>40507</t>
+          <t>40674</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>72128</t>
+          <t>71087</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -8672,12 +8672,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>291968</t>
+          <t>280547</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>425847</t>
+          <t>425486</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8687,12 +8687,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>228037</t>
+          <t>220202</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>326012</t>
+          <t>324946</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>551896</t>
+          <t>568641</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>725653</t>
+          <t>727485</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P78C_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P78C_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>217112</t>
+          <t>234410</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>199915</t>
+          <t>218754</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>232231</t>
+          <t>248670</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>214513</t>
+          <t>233618</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>205176</t>
+          <t>224184</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>221761</t>
+          <t>242116</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>431626</t>
+          <t>468028</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>411463</t>
+          <t>450886</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>449017</t>
+          <t>484326</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>560</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12698</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>670</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>670</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>839</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>839</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12412</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20942</t>
+          <t>23361</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>16977</t>
+          <t>19597</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25909</t>
+          <t>28798</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>871</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>511</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -1403,32 +1403,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>48726</t>
+          <t>45535</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36026</t>
+          <t>34907</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66522</t>
+          <t>58580</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,27 +1438,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26240</t>
+          <t>28476</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19977</t>
+          <t>20808</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34453</t>
+          <t>37400</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>74965</t>
+          <t>74011</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60882</t>
+          <t>58761</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95065</t>
+          <t>89965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -1516,17 +1516,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>287200</t>
+          <t>303108</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>287200</t>
+          <t>303108</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>287200</t>
+          <t>303108</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1551,17 +1551,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>246400</t>
+          <t>267559</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>246400</t>
+          <t>267559</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>246400</t>
+          <t>267559</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>533600</t>
+          <t>570667</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>533600</t>
+          <t>570667</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>533600</t>
+          <t>570667</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>403848</t>
+          <t>410909</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>386969</t>
+          <t>391144</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>418409</t>
+          <t>426407</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>330416</t>
+          <t>345125</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>321728</t>
+          <t>334666</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>338141</t>
+          <t>352956</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>734265</t>
+          <t>756034</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>715285</t>
+          <t>734754</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>750424</t>
+          <t>775474</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17571</t>
+          <t>20906</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>12922</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27759</t>
+          <t>34155</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>20076</t>
+          <t>23399</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12649</t>
+          <t>15545</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32105</t>
+          <t>36481</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>683</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>683</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>595</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>595</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>14912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>20799</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>14025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>722</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13586</t>
+          <t>15639</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -2311,32 +2311,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28445</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>22892</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42931</t>
+          <t>51215</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18647</t>
+          <t>20695</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11844</t>
+          <t>13866</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26620</t>
+          <t>29888</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>47092</t>
+          <t>55026</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34704</t>
+          <t>41475</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>60712</t>
+          <t>71151</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -2424,17 +2424,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>462450</t>
+          <t>480188</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>462450</t>
+          <t>480188</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>462450</t>
+          <t>480188</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>355940</t>
+          <t>374696</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>355940</t>
+          <t>374696</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>355940</t>
+          <t>374696</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>818390</t>
+          <t>854884</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>818390</t>
+          <t>854884</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>818390</t>
+          <t>854884</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>215312</t>
+          <t>220200</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200967</t>
+          <t>206552</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>227758</t>
+          <t>233567</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>238029</t>
+          <t>245997</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>226411</t>
+          <t>236293</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246215</t>
+          <t>255636</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>453340</t>
+          <t>466197</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>435929</t>
+          <t>446976</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>467422</t>
+          <t>480518</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15143</t>
+          <t>14726</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23096</t>
+          <t>21996</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9796</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>19972</t>
+          <t>19596</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14015</t>
+          <t>13268</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29507</t>
+          <t>27575</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>596</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>452</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,22 +2837,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>613</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,22 +2950,22 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -2993,32 +2993,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>10464</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19067</t>
+          <t>17913</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3028,32 +3028,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11517</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>17267</t>
+          <t>16994</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>10914</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26170</t>
+          <t>25562</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -3219,32 +3219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>34935</t>
+          <t>34429</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25969</t>
+          <t>25073</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>45447</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3254,32 +3254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>29315</t>
+          <t>29325</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22450</t>
+          <t>21117</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39862</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3289,32 +3289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>64250</t>
+          <t>63754</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>51983</t>
+          <t>51822</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>80001</t>
+          <t>79317</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -3332,17 +3332,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>281753</t>
+          <t>285204</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>281753</t>
+          <t>285204</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>281753</t>
+          <t>285204</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3367,17 +3367,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>279671</t>
+          <t>287787</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>279671</t>
+          <t>287787</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>279671</t>
+          <t>287787</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3402,17 +3402,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>561424</t>
+          <t>572991</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>561424</t>
+          <t>572991</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>561424</t>
+          <t>572991</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>192704</t>
+          <t>237763</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>172421</t>
+          <t>215439</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>212039</t>
+          <t>258660</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>246754</t>
+          <t>243490</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>129450</t>
+          <t>227554</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>309052</t>
+          <t>254456</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>439459</t>
+          <t>481253</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>311518</t>
+          <t>454519</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>500548</t>
+          <t>507824</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>76,57%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>24398</t>
+          <t>26203</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>15463</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41179</t>
+          <t>40647</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9730</t>
+          <t>11376</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16985</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>34128</t>
+          <t>37579</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20473</t>
+          <t>26219</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>53309</t>
+          <t>54188</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>2384</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>581</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,17 +3745,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -3788,32 +3788,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>8549</t>
+          <t>9512</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21185</t>
+          <t>22356</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3823,32 +3823,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3858,32 +3858,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>26927</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3911,12 +3911,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15449</t>
+          <t>16700</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3936,32 +3936,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>72854</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>215750</t>
+          <t>12354</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3971,32 +3971,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>75840</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>244594</t>
+          <t>19998</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -4014,32 +4014,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>9422</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15775</t>
+          <t>20961</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4049,32 +4049,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1576</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>9419</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4084,32 +4084,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>10271</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>7784</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>19776</t>
+          <t>25750</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -4127,32 +4127,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>52481</t>
+          <t>61286</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>38979</t>
+          <t>45868</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>67793</t>
+          <t>77801</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4162,32 +4162,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>41262</t>
+          <t>45922</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>23130</t>
+          <t>36301</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>60130</t>
+          <t>59592</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>93743</t>
+          <t>107208</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>63393</t>
+          <t>89877</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>118852</t>
+          <t>130525</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -4240,17 +4240,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>289401</t>
+          <t>350357</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>289401</t>
+          <t>350357</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>289401</t>
+          <t>350357</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>377395</t>
+          <t>312818</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>377395</t>
+          <t>312818</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>377395</t>
+          <t>312818</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>666797</t>
+          <t>663175</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>666797</t>
+          <t>663175</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>666797</t>
+          <t>663175</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>123025</t>
+          <t>143272</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>114551</t>
+          <t>133763</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>130433</t>
+          <t>152031</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>134276</t>
+          <t>147680</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>128230</t>
+          <t>141620</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>139464</t>
+          <t>153639</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>257301</t>
+          <t>290952</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>246404</t>
+          <t>280214</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>266484</t>
+          <t>301870</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>15961</t>
+          <t>17590</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>742</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>742</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -4809,32 +4809,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>10135</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>13415</t>
+          <t>16123</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4844,32 +4844,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>7169</t>
+          <t>7879</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4879,32 +4879,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>15449</t>
+          <t>18014</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>22029</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4932,12 +4932,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>441</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4992,32 +4992,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>441</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -5035,32 +5035,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>15808</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>20724</t>
+          <t>22949</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5070,32 +5070,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>5378</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5105,32 +5105,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>22379</t>
+          <t>24244</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>16173</t>
+          <t>16937</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>29337</t>
+          <t>31723</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -5148,17 +5148,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>155531</t>
+          <t>179952</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>155531</t>
+          <t>179952</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>155531</t>
+          <t>179952</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,17 +5183,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>153901</t>
+          <t>168604</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>153901</t>
+          <t>168604</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>153901</t>
+          <t>168604</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,17 +5218,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>309432</t>
+          <t>348556</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>309432</t>
+          <t>348556</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>309432</t>
+          <t>348556</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5265,32 +5265,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>172475</t>
+          <t>176176</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>159006</t>
+          <t>163170</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>184589</t>
+          <t>188671</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,32 +5300,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>165549</t>
+          <t>168731</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>156765</t>
+          <t>159103</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>173303</t>
+          <t>175866</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>338024</t>
+          <t>344907</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>322825</t>
+          <t>329892</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>351847</t>
+          <t>359502</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>78,34%</t>
         </is>
       </c>
     </row>
@@ -5378,32 +5378,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>13065</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5413,32 +5413,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>518</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5448,32 +5448,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>14709</t>
+          <t>15280</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>591</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5674,22 +5674,22 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>590</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -5717,32 +5717,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>32476</t>
+          <t>31725</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>24158</t>
+          <t>22815</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>42813</t>
+          <t>41126</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5752,32 +5752,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>8525</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>5052</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>13739</t>
+          <t>14083</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5787,32 +5787,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>41001</t>
+          <t>40772</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>31908</t>
+          <t>31969</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>53517</t>
+          <t>51594</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -5830,22 +5830,22 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>350</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>297</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5900,22 +5900,22 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>481</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -5943,32 +5943,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>35720</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>27919</t>
+          <t>26829</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>46606</t>
+          <t>46747</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5978,32 +5978,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>24093</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>17185</t>
+          <t>17513</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>31812</t>
+          <t>31881</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>60288</t>
+          <t>60138</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>47971</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>72897</t>
+          <t>72115</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -6056,17 +6056,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>251044</t>
+          <t>254062</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>251044</t>
+          <t>254062</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>251044</t>
+          <t>254062</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6091,17 +6091,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>200871</t>
+          <t>204835</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>200871</t>
+          <t>204835</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>200871</t>
+          <t>204835</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6126,17 +6126,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>451915</t>
+          <t>458897</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>451915</t>
+          <t>458897</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>451915</t>
+          <t>458897</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6173,32 +6173,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>397760</t>
+          <t>464171</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>374385</t>
+          <t>438666</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>416435</t>
+          <t>485797</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6208,32 +6208,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>606042</t>
+          <t>482220</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>553459</t>
+          <t>463772</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>668686</t>
+          <t>500246</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6243,32 +6243,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>1003802</t>
+          <t>946391</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>939845</t>
+          <t>916239</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1109504</t>
+          <t>977612</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -6286,32 +6286,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>55649</t>
+          <t>62591</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>43602</t>
+          <t>48077</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>71159</t>
+          <t>79292</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6321,32 +6321,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>25367</t>
+          <t>30055</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>9723</t>
+          <t>21309</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>39203</t>
+          <t>40606</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6356,32 +6356,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>81016</t>
+          <t>92645</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>44195</t>
+          <t>75782</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>105070</t>
+          <t>112824</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -6399,32 +6399,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>13736</t>
+          <t>15116</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6434,32 +6434,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>8212</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6469,32 +6469,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>10445</t>
+          <t>11799</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>19139</t>
+          <t>19419</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -6512,32 +6512,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>12991</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>18241</t>
+          <t>20743</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6547,32 +6547,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>14801</t>
+          <t>18543</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>18322</t>
+          <t>23121</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>15221</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>28224</t>
+          <t>33754</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -6625,32 +6625,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>18928</t>
+          <t>20746</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>12146</t>
+          <t>13543</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>28577</t>
+          <t>31039</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6660,32 +6660,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>25393</t>
+          <t>24537</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6695,32 +6695,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>34384</t>
+          <t>38440</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>19204</t>
+          <t>27969</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>47410</t>
+          <t>50364</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -6738,32 +6738,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>11954</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>17712</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6773,32 +6773,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>12418</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6808,32 +6808,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>16777</t>
+          <t>20206</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>8625</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>25571</t>
+          <t>29020</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -6851,32 +6851,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>55143</t>
+          <t>69661</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>42863</t>
+          <t>53666</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>72205</t>
+          <t>88666</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6886,32 +6886,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>54892</t>
+          <t>71407</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>23304</t>
+          <t>57726</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>82423</t>
+          <t>85489</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6921,32 +6921,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>110035</t>
+          <t>141068</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>65582</t>
+          <t>120002</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>140170</t>
+          <t>164284</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -6964,17 +6964,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>555200</t>
+          <t>649483</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>555200</t>
+          <t>649483</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>555200</t>
+          <t>649483</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6999,17 +6999,17 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>719581</t>
+          <t>624188</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>719581</t>
+          <t>624188</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>719581</t>
+          <t>624188</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7034,17 +7034,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>1274781</t>
+          <t>1273671</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>1274781</t>
+          <t>1273671</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>1274781</t>
+          <t>1273671</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7081,32 +7081,32 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>364919</t>
+          <t>427281</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>158936</t>
+          <t>400288</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>517396</t>
+          <t>454116</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7116,32 +7116,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>330501</t>
+          <t>383414</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>313300</t>
+          <t>364366</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>346508</t>
+          <t>401584</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7151,32 +7151,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>695421</t>
+          <t>810695</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>372945</t>
+          <t>775633</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>856917</t>
+          <t>844245</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -7194,32 +7194,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>109255</t>
+          <t>122661</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>52523</t>
+          <t>104661</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>162823</t>
+          <t>144283</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7229,32 +7229,32 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>48120</t>
+          <t>55261</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>37895</t>
+          <t>44021</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>60242</t>
+          <t>68216</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7264,32 +7264,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>157375</t>
+          <t>177922</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>82289</t>
+          <t>153778</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>199267</t>
+          <t>201095</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -7307,67 +7307,67 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>1424</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>9973</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>4336</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>1225</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>4320</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7377,32 +7377,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>11672</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -7420,32 +7420,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>250100</t>
+          <t>7738</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>580419</t>
+          <t>15269</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7455,32 +7455,32 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7490,32 +7490,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>254922</t>
+          <t>13091</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>7654</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>772532</t>
+          <t>21073</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -7533,32 +7533,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>24010</t>
+          <t>26861</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>17779</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>37366</t>
+          <t>37926</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7568,32 +7568,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>14648</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>20568</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7603,32 +7603,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>37056</t>
+          <t>41510</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>19150</t>
+          <t>30683</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>52344</t>
+          <t>55010</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -7646,32 +7646,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>14083</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>7676</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>23073</t>
+          <t>23432</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7716,32 +7716,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>23515</t>
+          <t>26040</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -7759,32 +7759,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>105152</t>
+          <t>120290</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>45001</t>
+          <t>101529</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>153368</t>
+          <t>143202</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7794,32 +7794,32 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>82540</t>
+          <t>93043</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>69699</t>
+          <t>79000</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>96166</t>
+          <t>109151</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7829,32 +7829,32 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>187692</t>
+          <t>213332</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>99281</t>
+          <t>190036</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>236144</t>
+          <t>239572</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -7872,17 +7872,17 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>869288</t>
+          <t>722445</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>869288</t>
+          <t>722445</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>869288</t>
+          <t>722445</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7907,17 +7907,17 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>481483</t>
+          <t>554500</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>481483</t>
+          <t>554500</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>481483</t>
+          <t>554500</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7942,17 +7942,17 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>1350771</t>
+          <t>1276945</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>1350771</t>
+          <t>1276945</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>1350771</t>
+          <t>1276945</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7989,32 +7989,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>2087155</t>
+          <t>2314184</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>1596478</t>
+          <t>2262136</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2276360</t>
+          <t>2367283</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8024,32 +8024,32 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2266081</t>
+          <t>2250273</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>2075468</t>
+          <t>2211681</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>2364798</t>
+          <t>2283320</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8059,32 +8059,32 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>4353236</t>
+          <t>4564456</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>3782930</t>
+          <t>4498822</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>4591892</t>
+          <t>4621627</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -8102,32 +8102,32 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>243015</t>
+          <t>268604</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>185726</t>
+          <t>237883</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>281936</t>
+          <t>301205</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8137,32 +8137,32 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>95687</t>
+          <t>109329</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>73254</t>
+          <t>93373</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>114745</t>
+          <t>129443</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8172,32 +8172,32 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>338702</t>
+          <t>377932</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>280631</t>
+          <t>345437</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>380516</t>
+          <t>417398</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -8215,32 +8215,32 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>25435</t>
+          <t>26436</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8250,32 +8250,32 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>11564</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8285,32 +8285,32 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>24190</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>13621</t>
+          <t>16410</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>32755</t>
+          <t>35487</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -8328,32 +8328,32 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>273758</t>
+          <t>34327</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>28073</t>
+          <t>23617</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>953297</t>
+          <t>51389</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8363,32 +8363,32 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>20503</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>11094</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>25922</t>
+          <t>29786</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8398,32 +8398,32 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>291017</t>
+          <t>54830</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>44681</t>
+          <t>41707</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>1061249</t>
+          <t>72658</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -8441,32 +8441,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>116824</t>
+          <t>125967</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>87237</t>
+          <t>106109</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>139646</t>
+          <t>151678</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8476,32 +8476,32 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>130947</t>
+          <t>68989</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>56850</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>403294</t>
+          <t>83122</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8511,32 +8511,32 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>247772</t>
+          <t>194956</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>170672</t>
+          <t>171611</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>553903</t>
+          <t>223804</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -8554,69 +8554,69 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>39949</t>
+          <t>47891</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>27375</t>
+          <t>35588</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>54130</t>
+          <t>64960</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>10699</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>24367</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
           <t>0,87%</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>14241</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>8501</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>21890</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O73" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="P73" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
           <t>71</t>
@@ -8624,32 +8624,32 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>54190</t>
+          <t>64641</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>40674</t>
+          <t>50422</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>71087</t>
+          <t>84221</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -8667,32 +8667,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>375339</t>
+          <t>417058</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>280547</t>
+          <t>381091</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>425486</t>
+          <t>458619</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8702,32 +8702,32 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>285105</t>
+          <t>321723</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>220202</t>
+          <t>294697</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>324946</t>
+          <t>351378</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8737,32 +8737,32 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>660444</t>
+          <t>738781</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>568641</t>
+          <t>691417</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>727485</t>
+          <t>785232</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -8780,17 +8780,17 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>3151867</t>
+          <t>3224800</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>3151867</t>
+          <t>3224800</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>3151867</t>
+          <t>3224800</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8815,17 +8815,17 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>2815243</t>
+          <t>2794987</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>2815243</t>
+          <t>2794987</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>2815243</t>
+          <t>2794987</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8850,17 +8850,17 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>5967110</t>
+          <t>6019786</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>5967110</t>
+          <t>6019786</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>5967110</t>
+          <t>6019786</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
